--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_578_Norway.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_578_Norway.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R44c3e5aeabb84d3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R658ba172ef5d4855"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rd33e58b97d234a94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R4844c3f8821d4f3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R2528e4a5cfb24ea9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R1c69fdea835343e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R9ef14213af8042cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R4964b7ef8ff841ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rebc7e4381bdf47a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R2fe1584d5e964649"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R9bba28b9513c480d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rd81a5d75e1c34986"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ578CommercialTable" displayName="EEZ578CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ578CommercialTable" displayName="EEZ578CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ578FunctionalTable" displayName="EEZ578FunctionalTable" ref="A1:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O26"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ578FunctionalTable" displayName="EEZ578FunctionalTable" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E26"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ578ValidationTable" displayName="EEZ578ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ578ValidationTable" displayName="EEZ578ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -15568,7 +15522,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b78ae6b398c431f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a4f93efca514465"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15578,20 +15532,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -15599,714 +15543,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.2427879896</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.2427879896</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$223,A2,'Species'!$U$2:$U$223))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>31.27715187586772</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>31.27715187586772</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>855625.0705192535</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.102026156252515</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1264.8125210373507</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>855625.0705192535</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1391.8519137808116</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$223,A3,'Species'!$U$2:$U$223))</x:f>
-        <x:v>1190903391.881065</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.102026156252515</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1264.8125210373507</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1082205302.506218</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>108698089.37484694</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1004412832972812</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.10044128329728119</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>21039.909062993698</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.131754913567432</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>135.4424850857104</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>21039.909062993698</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>165.904852584077</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$223,A4,'Species'!$U$2:$U$223))</x:f>
-        <x:v>3490623.0114783547</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.131754913567432</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>135.4424850857104</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>2849697.569469227</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>640925.4420091277</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.224909986545872</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.2249099865458719</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>25407.575865376402</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.023412621037497</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1055.389140200351</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>25407.575865376402</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1659.145668206157</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$223,A5,'Species'!$U$2:$U$223))</x:f>
-        <x:v>42154869.43665856</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.023412621037497</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1055.389140200351</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>26814879.64713479</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>15339989.789523773</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.5720700592875074</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.5720700592875073</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>573905.1467385307</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.378595246988477</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>239.1086277247831</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>573905.1467385307</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>239.36114504624868</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$223,A6,'Species'!$U$2:$U$223))</x:f>
-        <x:v>137370593.07127008</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.378595246988477</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>239.1086277247831</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>137225672.08084035</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>144920.99042972922</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.001056077833194</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0010560778331940362</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>590.0518182972</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.1109372700809783</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>12.910327821097075</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>590.0518182972</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>20.089454911085767</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$223,A7,'Species'!$U$2:$U$223))</x:f>
-        <x:v>11853.819398885771</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.1109372700809783</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>12.910327821097075</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>7617.762405651258</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>4236.056993234513</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.5560762816771474</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.5560762816771475</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>35465.1573602954</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.346683042359567</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>222.16878622862356</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>35465.1573602954</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>336.8511209867768</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$223,A8,'Species'!$U$2:$U$223))</x:f>
-        <x:v>11946478.012787944</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.346683042359567</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>222.16878622862356</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>7879250.964143964</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>4067227.0486439792</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.5161946315903214</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.5161946315903215</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>164392.53399160542</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.631482351820427</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>428.0380252933061</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>164392.53399160542</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>430.711968649825</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$223,A9,'Species'!$U$2:$U$223))</x:f>
-        <x:v>70805831.94685765</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.631482351820427</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>428.0380252933061</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>70366255.62272948</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>439576.32412816584</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0062469761995716</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.00624697619957165</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>439.7983496432</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.3661367131550413</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>232.34680943021567</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>439.7983496432</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>292.46376786610256</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$223,A10,'Species'!$U$2:$U$223))</x:f>
-        <x:v>128625.08243794387</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.3661367131550413</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>232.34680943021567</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>102185.74333227196</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>26439.339105671912</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.2587380415651577</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.2587380415651576</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>32570.0131389079</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.9020417260439215</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>798.0713604986238</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>32570.0131389079</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>863.1910449528784</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$223,A11,'Species'!$U$2:$U$223))</x:f>
-        <x:v>28114143.67550289</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.9020417260439215</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>798.0713604986238</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>25993194.69722628</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>2120948.9782766104</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.081596317920203</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.08159631792020301</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>815.2776206584</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.152798366857965</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1421.668585186447</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>815.2776206584</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1566.4650139251914</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$223,A12,'Species'!$U$2:$U$223))</x:f>
-        <x:v>1277103.8693975576</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.152798366857965</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1421.668585186447</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>1159054.5814956003</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>118049.28790195729</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1018496365802126</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.1018496365802126</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>62.7269090237</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.461357991440896</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2893.0636687784795</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>62.7269090237</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2896.5019990136498</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$223,A13,'Species'!$U$2:$U$223))</x:f>
-        <x:v>181688.61737909442</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.461357991440896</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2893.0636687784795</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>181472.94155123943</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>215.67582785498234</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0011884737526784</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.0011884737526783606</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf700198a59f148e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79ee60713268484f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16316,20 +15796,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -16337,1416 +15807,497 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>220.95031557410002</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.9533189482562245</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>898.088113217497</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>220.95031557410002</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>971.2655599171129</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$223,A2,'Species'!$U$2:$U$223))</x:f>
-        <x:v>214601.43196994104</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.9533189482562245</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>898.088113217497</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>198432.85202875405</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>16168.579941186996</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0814813664969352</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.08148136649693508</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1088.0961586186</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.417810962964518</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2617.043629583867</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1088.0961586186</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2653.8399217956357</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$223,A3,'Species'!$U$2:$U$223))</x:f>
-        <x:v>2887633.0244945167</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.417810962964518</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2617.043629583867</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2847595.120287484</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>40037.90420703264</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0140602517267239</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.014060251726723897</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>34.578900159499995</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.5400184494714715</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>346.7515806592886</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>34.578900159499995</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>346.79096007737024</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$223,A4,'Species'!$U$2:$U$223))</x:f>
-        <x:v>11991.649984732534</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.5400184494714715</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>346.7515806592886</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>11990.28828776635</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1.3616969661834446</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0001135666577403</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0001135666577402296</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>447438.5659353339</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.088230228580863</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1225.2655660108803</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>447438.5659353339</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1226.9835156551524</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$223,A5,'Species'!$U$2:$U$223))</x:f>
-        <x:v>548999744.6710356</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.088230228580863</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1225.2655660108803</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>548231067.7458535</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>768676.9251821041</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0014021039127583</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0014021039127582677</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>249007.6825091726</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.298013709453062</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1986.1576137671686</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>249007.6825091726</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2022.0833353600085</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$223,A6,'Species'!$U$2:$U$223))</x:f>
-        <x:v>503514285.17841375</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.298013709453062</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1986.1576137671686</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>494568504.50211096</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>8945780.67630279</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0180880516953028</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.018088051695302823</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>6085.578252052</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.2846162625694895</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>192.58225273546992</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>6085.578252052</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>220.20812540730233</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$223,A7,'Species'!$U$2:$U$223))</x:f>
-        <x:v>1340093.7789038185</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.2846162625694895</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>192.58225273546992</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1171974.3689781574</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>168119.40992566105</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1434497326697035</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.14344973266970343</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>48.5880424247</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.447528561151129</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2802.3899133244877</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>48.5880424247</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2812.51202563523</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$223,A8,'Species'!$U$2:$U$223))</x:f>
-        <x:v>136654.4536215435</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.447528561151129</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2802.3899133244877</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>136162.63999916156</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>491.8136223819456</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0036119571593571</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0036119571593571775</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>24.5623388667</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6762996540532544</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>474.5693151625494</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>24.5623388667</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>507.94039153794023</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$223,A9,'Species'!$U$2:$U$223))</x:f>
-        <x:v>12476.204021039164</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6762996540532544</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>474.5693151625494</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>11656.532334760288</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>819.6716862788762</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.070318655903744</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.07031865590374416</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1556.4671238767</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.7867721069257083</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>612.0291493156113</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1556.4671238767</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>614.2796054562402</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$223,A10,'Species'!$U$2:$U$223))</x:f>
-        <x:v>956106.0107605883</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.7867721069257083</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>612.0291493156113</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>952603.2497639729</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>3502.7609966153977</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0036770407800764</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0036770407800763632</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>633.6573250591999</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.241873814996543</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1745.3149749965237</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>633.6573250591999</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1799.850926127152</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$223,A11,'Species'!$U$2:$U$223))</x:f>
-        <x:v>1140488.7233550549</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.241873814996543</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1745.3149749965237</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1105931.6184420616</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>34557.104912993265</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0312470539197298</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.03124705391972991</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>7036.193404469499</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.2623269960395116</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>182.94771773006636</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>7036.193404469499</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>263.5188665068759</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$223,A12,'Species'!$U$2:$U$223))</x:f>
-        <x:v>1854169.7104689586</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.2623269960395116</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>182.94771773006636</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>1287255.5248550405</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>566914.1856139181</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.4404053233158653</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.4404053233158654</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>1249.9128219315003</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.227720009174457</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1689.3514510419145</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>1249.9128219315003</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2337.939610093415</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$223,A13,'Species'!$U$2:$U$223))</x:f>
-        <x:v>2922220.6955572916</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.227720009174457</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1689.3514510419145</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>2111542.039405874</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>810678.6561514176</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.383927310478516</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.3839273104785159</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>10377.586517186699</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.650751824439762</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>447.45753357901384</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>10377.586517186699</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>448.004671554643</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$223,A14,'Species'!$U$2:$U$223))</x:f>
-        <x:v>4649207.239162118</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.650751824439762</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>447.45753357901384</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>4643529.267483189</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>5677.971678929403</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0012227707314543</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.0012227707314542</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>75388.55710607549</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.5914702254093944</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>390.3644187801077</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>75388.55710607549</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>607.9289573676855</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$223,A15,'Species'!$U$2:$U$223))</x:f>
-        <x:v>45830886.91895069</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.5914702254093944</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>390.3644187801077</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>29429010.277384117</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>16401876.641566575</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.5573370115736187</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.5573370115736187</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>142643.55858350487</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.8534678081888463</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>713.621306421867</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>142643.55858350487</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>864.3046233619699</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$223,A16,'Species'!$U$2:$U$223))</x:f>
-        <x:v>123287487.17652726</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.8534678081888463</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>713.621306421867</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>101793482.62902486</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>21494004.5475024</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.2111530521638103</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.21115305216381025</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>731024.8870393122</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.4351047404391744</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>272.33580314165596</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>731024.8870393122</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>281.5048420387354</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$223,A17,'Species'!$U$2:$U$223))</x:f>
-        <x:v>205787045.35238594</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.4351047404391744</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>272.33580314165596</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>199084249.7283894</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>6702795.623996526</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0336681361440754</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.033668136144075426</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>4.4427612275</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.2002650210823202</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>158.5860642684522</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>4.4427612275</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>158.636552230805</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$223,A18,'Species'!$U$2:$U$223))</x:f>
-        <x:v>704.7843235152991</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.2002650210823202</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>158.5860642684522</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>704.5600175537026</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0.22430596159654215</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0003183631713524</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.00031836317135246076</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>622.5148263478001</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.131311963865475</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>13.530441373926084</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>622.5148263478001</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>20.708126921520744</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$223,A19,'Species'!$U$2:$U$223))</x:f>
-        <x:v>12891.11603453869</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.131311963865475</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>13.530441373926084</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>8422.900362298686</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>4468.215672240005</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.5304842132812062</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.5304842132812062</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>14003.715658524201</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.0661487239031446</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>116.45247519873567</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>14003.715658524201</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>116.85850676447217</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$223,A20,'Species'!$U$2:$U$223))</x:f>
-        <x:v>1636453.3010093952</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.0661487239031446</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>116.45247519873567</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>1630767.3504144358</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>5685.950594959315</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.003486671837963</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.0034866718379628543</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>0.0289266252</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.31</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>204.17379446695296</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>0.0289266252</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$223,A21,'Species'!$U$2:$U$223))</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>5.906058828207382</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.31</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
-        <x:v>5.906058828207382</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>2341.2133017058</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.0259275235380936</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>106.15183928079462</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>2341.2133017058</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>106.86856038747834</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$223,A22,'Species'!$U$2:$U$223))</x:f>
-        <x:v>250202.09511331382</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.0259275235380936</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>106.15183928079462</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>248524.09812473258</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>1677.9969885812316</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0067518482160995</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.006751848216099575</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>3.1107444696</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.477919255753645</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>300.5517463376459</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>3.1107444696</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>311.71941857011274</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$223,A23,'Species'!$U$2:$U$223))</x:f>
-        <x:v>969.6794573839057</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.477919255753645</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>300.5517463376459</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>934.9396827484542</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>34.73977463545157</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0371572362115666</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.037157236211566726</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>19321.9976133244</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>4.2561009352461525</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>1803.4368325054802</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>19321.9976133244</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>2112.3476192549047</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$223,A24,'Species'!$U$2:$U$223))</x:f>
-        <x:v>40814775.65775475</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>4.2561009352461525</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>1803.4368325054802</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>34846002.173452206</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>5968773.484302543</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.1712900508526605</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.17129005085266039</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>150.0467220179</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.870179331203528</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>741.6164103042997</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>150.0467220179</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>796.4630188244146</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$223,A25,'Species'!$U$2:$U$223))</x:f>
-        <x:v>119506.66518308439</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.870179331203528</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>741.6164103042997</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>111277.11136084214</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>8229.553822242247</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.0739554947248404</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.07395549472484048</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>7.0112347146000005</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.82</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>660.6934480075957</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>7.0112347146000005</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>660.6934480075957</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$223,A26,'Species'!$U$2:$U$223))</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>4632.276838379626</x:v>
       </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.82</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>660.6934480075957</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
-        <x:v>4632.276838379626</x:v>
-      </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G26">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O26">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ad2fc07ce554fad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9cf1d9d43f574db2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17921,7 +16472,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -18020,7 +16571,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>1486385233.701386</x:v>
+        <x:v>1354784615.3936987</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -18034,7 +16585,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>1486385233.701386</x:v>
+        <x:v>1424436259.700941</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -18048,7 +16599,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-131600618.30768728</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -18062,7 +16613,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-61948974.00044489</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -18073,9 +16624,9 @@
         <x:v>EEZ_578</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -18087,47 +16638,19 @@
         <x:v>EEZ_578</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_578</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_578</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d6f1c8a37a14993"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3dc7460930264aa9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18174,7 +16697,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
